--- a/P012-excavator-split_data_files/17_05_2017_cherinet_bisetegn _excavator_records_part_4.xlsx
+++ b/P012-excavator-split_data_files/17_05_2017_cherinet_bisetegn _excavator_records_part_4.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="excavator" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="mpdm" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="daily_variables" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="excavator" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="mpdm" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="daily_variables" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1170,7 +1170,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z106"/>
+  <dimension ref="A1:Z111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11.875" customWidth="1" min="1" max="1"/>
@@ -1966,7 +1966,9 @@
       <c r="S12" s="10" t="n"/>
       <c r="U12" s="10" t="n"/>
       <c r="V12" s="10" t="n"/>
-      <c r="W12" s="10" t="n"/>
+      <c r="W12" s="10" t="n">
+        <v>423</v>
+      </c>
       <c r="X12" s="10" t="n"/>
       <c r="Y12" s="10" t="n"/>
       <c r="Z12" s="10" t="n"/>
@@ -2023,7 +2025,9 @@
       <c r="S13" s="10" t="n"/>
       <c r="U13" s="10" t="n"/>
       <c r="V13" s="10" t="n"/>
-      <c r="W13" s="10" t="n"/>
+      <c r="W13" s="10" t="n">
+        <v>423</v>
+      </c>
       <c r="X13" s="10" t="n"/>
       <c r="Y13" s="10" t="n"/>
       <c r="Z13" s="10" t="n"/>
@@ -2080,7 +2084,9 @@
       <c r="S14" s="10" t="n"/>
       <c r="U14" s="10" t="n"/>
       <c r="V14" s="10" t="n"/>
-      <c r="W14" s="10" t="n"/>
+      <c r="W14" s="10" t="n">
+        <v>423</v>
+      </c>
       <c r="X14" s="10" t="n"/>
       <c r="Y14" s="10" t="n"/>
       <c r="Z14" s="10" t="n"/>
@@ -2137,7 +2143,9 @@
       <c r="S15" s="10" t="n"/>
       <c r="U15" s="10" t="n"/>
       <c r="V15" s="10" t="n"/>
-      <c r="W15" s="10" t="n"/>
+      <c r="W15" s="10" t="n">
+        <v>423</v>
+      </c>
       <c r="X15" s="10" t="n"/>
       <c r="Y15" s="10" t="n"/>
       <c r="Z15" s="10" t="n"/>
@@ -2194,7 +2202,9 @@
       <c r="S16" s="10" t="n"/>
       <c r="U16" s="10" t="n"/>
       <c r="V16" s="10" t="n"/>
-      <c r="W16" s="10" t="n"/>
+      <c r="W16" s="10" t="n">
+        <v>423</v>
+      </c>
       <c r="X16" s="10" t="n"/>
       <c r="Y16" s="10" t="n"/>
       <c r="Z16" s="10" t="n"/>
@@ -2251,7 +2261,9 @@
       <c r="S17" s="10" t="n"/>
       <c r="U17" s="10" t="n"/>
       <c r="V17" s="10" t="n"/>
-      <c r="W17" s="10" t="n"/>
+      <c r="W17" s="10" t="n">
+        <v>423</v>
+      </c>
       <c r="X17" s="10" t="n"/>
       <c r="Y17" s="10" t="n"/>
       <c r="Z17" s="10" t="n"/>
@@ -2308,7 +2320,9 @@
       <c r="S18" s="10" t="n"/>
       <c r="U18" s="10" t="n"/>
       <c r="V18" s="10" t="n"/>
-      <c r="W18" s="10" t="n"/>
+      <c r="W18" s="10" t="n">
+        <v>423</v>
+      </c>
       <c r="X18" s="10" t="n"/>
       <c r="Y18" s="10" t="n"/>
       <c r="Z18" s="10" t="n"/>
@@ -2365,7 +2379,9 @@
       <c r="S19" s="10" t="n"/>
       <c r="U19" s="10" t="n"/>
       <c r="V19" s="10" t="n"/>
-      <c r="W19" s="10" t="n"/>
+      <c r="W19" s="10" t="n">
+        <v>423</v>
+      </c>
       <c r="X19" s="10" t="n"/>
       <c r="Y19" s="10" t="n"/>
       <c r="Z19" s="10" t="n"/>
@@ -2422,7 +2438,9 @@
       <c r="S20" s="10" t="n"/>
       <c r="U20" s="10" t="n"/>
       <c r="V20" s="10" t="n"/>
-      <c r="W20" s="10" t="n"/>
+      <c r="W20" s="10" t="n">
+        <v>423</v>
+      </c>
       <c r="X20" s="10" t="n"/>
       <c r="Y20" s="10" t="n"/>
       <c r="Z20" s="10" t="n"/>
@@ -2479,7 +2497,9 @@
       <c r="S21" s="10" t="n"/>
       <c r="U21" s="10" t="n"/>
       <c r="V21" s="10" t="n"/>
-      <c r="W21" s="10" t="n"/>
+      <c r="W21" s="10" t="n">
+        <v>423</v>
+      </c>
       <c r="X21" s="10" t="n"/>
       <c r="Y21" s="10" t="n"/>
       <c r="Z21" s="10" t="n"/>
@@ -2536,7 +2556,9 @@
       <c r="S22" s="10" t="n"/>
       <c r="U22" s="10" t="n"/>
       <c r="V22" s="10" t="n"/>
-      <c r="W22" s="10" t="n"/>
+      <c r="W22" s="10" t="n">
+        <v>423</v>
+      </c>
       <c r="X22" s="10" t="n"/>
       <c r="Y22" s="10" t="n"/>
       <c r="Z22" s="10" t="n"/>
@@ -2593,7 +2615,9 @@
       <c r="S23" s="10" t="n"/>
       <c r="U23" s="10" t="n"/>
       <c r="V23" s="10" t="n"/>
-      <c r="W23" s="10" t="n"/>
+      <c r="W23" s="10" t="n">
+        <v>423</v>
+      </c>
       <c r="X23" s="10" t="n"/>
       <c r="Y23" s="10" t="n"/>
       <c r="Z23" s="10" t="n"/>
@@ -2650,7 +2674,9 @@
       <c r="S24" s="10" t="n"/>
       <c r="U24" s="10" t="n"/>
       <c r="V24" s="10" t="n"/>
-      <c r="W24" s="10" t="n"/>
+      <c r="W24" s="10" t="n">
+        <v>423</v>
+      </c>
       <c r="X24" s="10" t="n"/>
       <c r="Y24" s="10" t="n"/>
       <c r="Z24" s="10" t="n"/>
@@ -2707,7 +2733,9 @@
       <c r="S25" s="10" t="n"/>
       <c r="U25" s="10" t="n"/>
       <c r="V25" s="10" t="n"/>
-      <c r="W25" s="10" t="n"/>
+      <c r="W25" s="10" t="n">
+        <v>423</v>
+      </c>
       <c r="X25" s="10" t="n"/>
       <c r="Y25" s="10" t="n"/>
       <c r="Z25" s="10" t="n"/>
@@ -2764,7 +2792,9 @@
       <c r="S26" s="10" t="n"/>
       <c r="U26" s="10" t="n"/>
       <c r="V26" s="10" t="n"/>
-      <c r="W26" s="10" t="n"/>
+      <c r="W26" s="10" t="n">
+        <v>423</v>
+      </c>
       <c r="X26" s="10" t="n"/>
       <c r="Y26" s="10" t="n"/>
       <c r="Z26" s="10" t="n"/>
@@ -2821,7 +2851,9 @@
       <c r="S27" s="10" t="n"/>
       <c r="U27" s="10" t="n"/>
       <c r="V27" s="10" t="n"/>
-      <c r="W27" s="10" t="n"/>
+      <c r="W27" s="10" t="n">
+        <v>423</v>
+      </c>
       <c r="X27" s="10" t="n"/>
       <c r="Y27" s="10" t="n"/>
       <c r="Z27" s="10" t="n"/>
@@ -2878,7 +2910,9 @@
       <c r="S28" s="10" t="n"/>
       <c r="U28" s="10" t="n"/>
       <c r="V28" s="10" t="n"/>
-      <c r="W28" s="10" t="n"/>
+      <c r="W28" s="10" t="n">
+        <v>423</v>
+      </c>
       <c r="X28" s="10" t="n"/>
       <c r="Y28" s="10" t="n"/>
       <c r="Z28" s="10" t="n"/>
@@ -2935,7 +2969,9 @@
       <c r="S29" s="10" t="n"/>
       <c r="U29" s="10" t="n"/>
       <c r="V29" s="10" t="n"/>
-      <c r="W29" s="10" t="n"/>
+      <c r="W29" s="10" t="n">
+        <v>423</v>
+      </c>
       <c r="X29" s="10" t="n"/>
       <c r="Y29" s="10" t="n"/>
       <c r="Z29" s="10" t="n"/>
@@ -2992,7 +3028,9 @@
       <c r="S30" s="10" t="n"/>
       <c r="U30" s="10" t="n"/>
       <c r="V30" s="10" t="n"/>
-      <c r="W30" s="10" t="n"/>
+      <c r="W30" s="10" t="n">
+        <v>423</v>
+      </c>
       <c r="X30" s="10" t="n"/>
       <c r="Y30" s="10" t="n"/>
       <c r="Z30" s="10" t="n"/>
@@ -3049,7 +3087,9 @@
       <c r="S31" s="10" t="n"/>
       <c r="U31" s="10" t="n"/>
       <c r="V31" s="10" t="n"/>
-      <c r="W31" s="10" t="n"/>
+      <c r="W31" s="10" t="n">
+        <v>423</v>
+      </c>
       <c r="X31" s="10" t="n"/>
       <c r="Y31" s="10" t="n"/>
       <c r="Z31" s="10" t="n"/>
@@ -3106,7 +3146,9 @@
       <c r="S32" s="10" t="n"/>
       <c r="U32" s="10" t="n"/>
       <c r="V32" s="10" t="n"/>
-      <c r="W32" s="10" t="n"/>
+      <c r="W32" s="10" t="n">
+        <v>423</v>
+      </c>
       <c r="X32" s="10" t="n"/>
       <c r="Y32" s="10" t="n"/>
       <c r="Z32" s="10" t="n"/>
@@ -3163,7 +3205,9 @@
       <c r="S33" s="10" t="n"/>
       <c r="U33" s="10" t="n"/>
       <c r="V33" s="10" t="n"/>
-      <c r="W33" s="10" t="n"/>
+      <c r="W33" s="10" t="n">
+        <v>423</v>
+      </c>
       <c r="X33" s="10" t="n"/>
       <c r="Y33" s="10" t="n"/>
       <c r="Z33" s="10" t="n"/>
@@ -3220,7 +3264,9 @@
       <c r="S34" s="10" t="n"/>
       <c r="U34" s="10" t="n"/>
       <c r="V34" s="10" t="n"/>
-      <c r="W34" s="10" t="n"/>
+      <c r="W34" s="10" t="n">
+        <v>423</v>
+      </c>
       <c r="X34" s="10" t="n"/>
       <c r="Y34" s="10" t="n"/>
       <c r="Z34" s="10" t="n"/>
@@ -3277,7 +3323,9 @@
       <c r="S35" s="10" t="n"/>
       <c r="U35" s="10" t="n"/>
       <c r="V35" s="10" t="n"/>
-      <c r="W35" s="10" t="n"/>
+      <c r="W35" s="10" t="n">
+        <v>423</v>
+      </c>
       <c r="X35" s="10" t="n"/>
       <c r="Y35" s="10" t="n"/>
       <c r="Z35" s="10" t="n"/>
@@ -3334,7 +3382,9 @@
       <c r="S36" s="10" t="n"/>
       <c r="U36" s="10" t="n"/>
       <c r="V36" s="10" t="n"/>
-      <c r="W36" s="10" t="n"/>
+      <c r="W36" s="10" t="n">
+        <v>423</v>
+      </c>
       <c r="X36" s="10" t="n"/>
       <c r="Y36" s="10" t="n"/>
       <c r="Z36" s="10" t="n"/>
@@ -3391,7 +3441,9 @@
       <c r="S37" s="10" t="n"/>
       <c r="U37" s="10" t="n"/>
       <c r="V37" s="10" t="n"/>
-      <c r="W37" s="10" t="n"/>
+      <c r="W37" s="10" t="n">
+        <v>423</v>
+      </c>
       <c r="X37" s="10" t="n"/>
       <c r="Y37" s="10" t="n"/>
       <c r="Z37" s="10" t="n"/>
@@ -3448,7 +3500,9 @@
       <c r="S38" s="10" t="n"/>
       <c r="U38" s="10" t="n"/>
       <c r="V38" s="10" t="n"/>
-      <c r="W38" s="10" t="n"/>
+      <c r="W38" s="10" t="n">
+        <v>423</v>
+      </c>
       <c r="X38" s="10" t="n"/>
       <c r="Y38" s="10" t="n"/>
       <c r="Z38" s="10" t="n"/>
@@ -3505,7 +3559,9 @@
       <c r="S39" s="10" t="n"/>
       <c r="U39" s="10" t="n"/>
       <c r="V39" s="10" t="n"/>
-      <c r="W39" s="10" t="n"/>
+      <c r="W39" s="10" t="n">
+        <v>423</v>
+      </c>
       <c r="X39" s="10" t="n"/>
       <c r="Y39" s="10" t="n"/>
       <c r="Z39" s="10" t="n"/>
@@ -3562,7 +3618,9 @@
       <c r="S40" s="10" t="n"/>
       <c r="U40" s="10" t="n"/>
       <c r="V40" s="10" t="n"/>
-      <c r="W40" s="10" t="n"/>
+      <c r="W40" s="10" t="n">
+        <v>423</v>
+      </c>
       <c r="X40" s="10" t="n"/>
       <c r="Y40" s="10" t="n"/>
       <c r="Z40" s="10" t="n"/>
@@ -3619,7 +3677,9 @@
       <c r="S41" s="10" t="n"/>
       <c r="U41" s="10" t="n"/>
       <c r="V41" s="10" t="n"/>
-      <c r="W41" s="10" t="n"/>
+      <c r="W41" s="10" t="n">
+        <v>423</v>
+      </c>
       <c r="X41" s="10" t="n"/>
       <c r="Y41" s="10" t="n"/>
       <c r="Z41" s="10" t="n"/>
@@ -3676,7 +3736,9 @@
       <c r="S42" s="10" t="n"/>
       <c r="U42" s="10" t="n"/>
       <c r="V42" s="10" t="n"/>
-      <c r="W42" s="10" t="n"/>
+      <c r="W42" s="10" t="n">
+        <v>423</v>
+      </c>
       <c r="X42" s="10" t="n"/>
       <c r="Y42" s="10" t="n"/>
       <c r="Z42" s="10" t="n"/>
@@ -3733,7 +3795,9 @@
       <c r="S43" s="10" t="n"/>
       <c r="U43" s="10" t="n"/>
       <c r="V43" s="10" t="n"/>
-      <c r="W43" s="10" t="n"/>
+      <c r="W43" s="10" t="n">
+        <v>423</v>
+      </c>
       <c r="X43" s="10" t="n"/>
       <c r="Y43" s="10" t="n"/>
       <c r="Z43" s="10" t="n"/>
@@ -3790,7 +3854,9 @@
       <c r="S44" s="10" t="n"/>
       <c r="U44" s="10" t="n"/>
       <c r="V44" s="10" t="n"/>
-      <c r="W44" s="10" t="n"/>
+      <c r="W44" s="10" t="n">
+        <v>423</v>
+      </c>
       <c r="X44" s="10" t="n"/>
       <c r="Y44" s="10" t="n"/>
       <c r="Z44" s="10" t="n"/>
@@ -3847,7 +3913,9 @@
       <c r="S45" s="10" t="n"/>
       <c r="U45" s="10" t="n"/>
       <c r="V45" s="10" t="n"/>
-      <c r="W45" s="10" t="n"/>
+      <c r="W45" s="10" t="n">
+        <v>423</v>
+      </c>
       <c r="X45" s="10" t="n"/>
       <c r="Y45" s="10" t="n"/>
       <c r="Z45" s="10" t="n"/>
@@ -3904,7 +3972,9 @@
       <c r="S46" s="10" t="n"/>
       <c r="U46" s="10" t="n"/>
       <c r="V46" s="10" t="n"/>
-      <c r="W46" s="10" t="n"/>
+      <c r="W46" s="10" t="n">
+        <v>423</v>
+      </c>
       <c r="X46" s="10" t="n"/>
       <c r="Y46" s="10" t="n"/>
       <c r="Z46" s="10" t="n"/>
@@ -3961,7 +4031,9 @@
       <c r="S47" s="10" t="n"/>
       <c r="U47" s="10" t="n"/>
       <c r="V47" s="10" t="n"/>
-      <c r="W47" s="10" t="n"/>
+      <c r="W47" s="10" t="n">
+        <v>423</v>
+      </c>
       <c r="X47" s="10" t="n"/>
       <c r="Y47" s="10" t="n"/>
       <c r="Z47" s="10" t="n"/>
@@ -4018,7 +4090,9 @@
       <c r="S48" s="10" t="n"/>
       <c r="U48" s="10" t="n"/>
       <c r="V48" s="10" t="n"/>
-      <c r="W48" s="10" t="n"/>
+      <c r="W48" s="10" t="n">
+        <v>423</v>
+      </c>
       <c r="X48" s="10" t="n"/>
       <c r="Y48" s="10" t="n"/>
       <c r="Z48" s="10" t="n"/>
@@ -4075,7 +4149,9 @@
       <c r="S49" s="10" t="n"/>
       <c r="U49" s="10" t="n"/>
       <c r="V49" s="10" t="n"/>
-      <c r="W49" s="10" t="n"/>
+      <c r="W49" s="10" t="n">
+        <v>423</v>
+      </c>
       <c r="X49" s="10" t="n"/>
       <c r="Y49" s="10" t="n"/>
       <c r="Z49" s="10" t="n"/>
@@ -4132,7 +4208,9 @@
       <c r="S50" s="10" t="n"/>
       <c r="U50" s="10" t="n"/>
       <c r="V50" s="10" t="n"/>
-      <c r="W50" s="10" t="n"/>
+      <c r="W50" s="10" t="n">
+        <v>423</v>
+      </c>
       <c r="X50" s="10" t="n"/>
       <c r="Y50" s="10" t="n"/>
       <c r="Z50" s="10" t="n"/>
@@ -4189,7 +4267,9 @@
       <c r="S51" s="10" t="n"/>
       <c r="U51" s="10" t="n"/>
       <c r="V51" s="10" t="n"/>
-      <c r="W51" s="10" t="n"/>
+      <c r="W51" s="10" t="n">
+        <v>423</v>
+      </c>
       <c r="X51" s="10" t="n"/>
       <c r="Y51" s="10" t="n"/>
       <c r="Z51" s="10" t="n"/>
@@ -4246,7 +4326,9 @@
       <c r="S52" s="10" t="n"/>
       <c r="U52" s="10" t="n"/>
       <c r="V52" s="10" t="n"/>
-      <c r="W52" s="10" t="n"/>
+      <c r="W52" s="10" t="n">
+        <v>423</v>
+      </c>
       <c r="X52" s="10" t="n"/>
       <c r="Y52" s="10" t="n"/>
       <c r="Z52" s="10" t="n"/>
@@ -4303,7 +4385,9 @@
       <c r="S53" s="10" t="n"/>
       <c r="U53" s="10" t="n"/>
       <c r="V53" s="10" t="n"/>
-      <c r="W53" s="10" t="n"/>
+      <c r="W53" s="10" t="n">
+        <v>423</v>
+      </c>
       <c r="X53" s="10" t="n"/>
       <c r="Y53" s="10" t="n"/>
       <c r="Z53" s="10" t="n"/>
@@ -4360,7 +4444,9 @@
       <c r="S54" s="10" t="n"/>
       <c r="U54" s="10" t="n"/>
       <c r="V54" s="10" t="n"/>
-      <c r="W54" s="10" t="n"/>
+      <c r="W54" s="10" t="n">
+        <v>423</v>
+      </c>
       <c r="X54" s="10" t="n"/>
       <c r="Y54" s="10" t="n"/>
       <c r="Z54" s="10" t="n"/>
@@ -4417,7 +4503,9 @@
       <c r="S55" s="10" t="n"/>
       <c r="U55" s="10" t="n"/>
       <c r="V55" s="10" t="n"/>
-      <c r="W55" s="10" t="n"/>
+      <c r="W55" s="10" t="n">
+        <v>423</v>
+      </c>
       <c r="X55" s="10" t="n"/>
       <c r="Y55" s="10" t="n"/>
       <c r="Z55" s="10" t="n"/>
@@ -4474,7 +4562,9 @@
       <c r="S56" s="10" t="n"/>
       <c r="U56" s="10" t="n"/>
       <c r="V56" s="10" t="n"/>
-      <c r="W56" s="10" t="n"/>
+      <c r="W56" s="10" t="n">
+        <v>423</v>
+      </c>
       <c r="X56" s="10" t="n"/>
       <c r="Y56" s="10" t="n"/>
       <c r="Z56" s="10" t="n"/>
@@ -4531,7 +4621,9 @@
       <c r="S57" s="10" t="n"/>
       <c r="U57" s="10" t="n"/>
       <c r="V57" s="10" t="n"/>
-      <c r="W57" s="10" t="n"/>
+      <c r="W57" s="10" t="n">
+        <v>423</v>
+      </c>
       <c r="X57" s="10" t="n"/>
       <c r="Y57" s="10" t="n"/>
       <c r="Z57" s="10" t="n"/>
@@ -4588,7 +4680,9 @@
       <c r="S58" s="10" t="n"/>
       <c r="U58" s="10" t="n"/>
       <c r="V58" s="10" t="n"/>
-      <c r="W58" s="10" t="n"/>
+      <c r="W58" s="10" t="n">
+        <v>423</v>
+      </c>
       <c r="X58" s="10" t="n"/>
       <c r="Y58" s="10" t="n"/>
       <c r="Z58" s="10" t="n"/>
@@ -4645,7 +4739,9 @@
       <c r="S59" s="10" t="n"/>
       <c r="U59" s="10" t="n"/>
       <c r="V59" s="10" t="n"/>
-      <c r="W59" s="10" t="n"/>
+      <c r="W59" s="10" t="n">
+        <v>423</v>
+      </c>
       <c r="X59" s="10" t="n"/>
       <c r="Y59" s="10" t="n"/>
       <c r="Z59" s="10" t="n"/>
@@ -4702,7 +4798,9 @@
       <c r="S60" s="10" t="n"/>
       <c r="U60" s="10" t="n"/>
       <c r="V60" s="10" t="n"/>
-      <c r="W60" s="10" t="n"/>
+      <c r="W60" s="10" t="n">
+        <v>423</v>
+      </c>
       <c r="X60" s="10" t="n"/>
       <c r="Y60" s="10" t="n"/>
       <c r="Z60" s="10" t="n"/>
@@ -4759,7 +4857,9 @@
       <c r="S61" s="10" t="n"/>
       <c r="U61" s="10" t="n"/>
       <c r="V61" s="10" t="n"/>
-      <c r="W61" s="10" t="n"/>
+      <c r="W61" s="10" t="n">
+        <v>423</v>
+      </c>
       <c r="X61" s="10" t="n"/>
       <c r="Y61" s="10" t="n"/>
       <c r="Z61" s="10" t="n"/>
@@ -4816,7 +4916,9 @@
       <c r="S62" s="10" t="n"/>
       <c r="U62" s="10" t="n"/>
       <c r="V62" s="10" t="n"/>
-      <c r="W62" s="10" t="n"/>
+      <c r="W62" s="10" t="n">
+        <v>423</v>
+      </c>
       <c r="X62" s="10" t="n"/>
       <c r="Y62" s="10" t="n"/>
       <c r="Z62" s="10" t="n"/>
@@ -4873,7 +4975,9 @@
       <c r="S63" s="10" t="n"/>
       <c r="U63" s="10" t="n"/>
       <c r="V63" s="10" t="n"/>
-      <c r="W63" s="10" t="n"/>
+      <c r="W63" s="10" t="n">
+        <v>423</v>
+      </c>
       <c r="X63" s="10" t="n"/>
       <c r="Y63" s="10" t="n"/>
       <c r="Z63" s="10" t="n"/>
@@ -4930,7 +5034,9 @@
       <c r="S64" s="10" t="n"/>
       <c r="U64" s="10" t="n"/>
       <c r="V64" s="10" t="n"/>
-      <c r="W64" s="10" t="n"/>
+      <c r="W64" s="10" t="n">
+        <v>423</v>
+      </c>
       <c r="X64" s="10" t="n"/>
       <c r="Y64" s="10" t="n"/>
       <c r="Z64" s="10" t="n"/>
@@ -4987,7 +5093,9 @@
       <c r="S65" s="10" t="n"/>
       <c r="U65" s="10" t="n"/>
       <c r="V65" s="10" t="n"/>
-      <c r="W65" s="10" t="n"/>
+      <c r="W65" s="10" t="n">
+        <v>423</v>
+      </c>
       <c r="X65" s="10" t="n"/>
       <c r="Y65" s="10" t="n"/>
       <c r="Z65" s="10" t="n"/>
@@ -5044,7 +5152,9 @@
       <c r="S66" s="10" t="n"/>
       <c r="U66" s="10" t="n"/>
       <c r="V66" s="10" t="n"/>
-      <c r="W66" s="10" t="n"/>
+      <c r="W66" s="10" t="n">
+        <v>423</v>
+      </c>
       <c r="X66" s="10" t="n"/>
       <c r="Y66" s="10" t="n"/>
       <c r="Z66" s="10" t="n"/>
@@ -5101,7 +5211,9 @@
       <c r="S67" s="10" t="n"/>
       <c r="U67" s="10" t="n"/>
       <c r="V67" s="10" t="n"/>
-      <c r="W67" s="10" t="n"/>
+      <c r="W67" s="10" t="n">
+        <v>423</v>
+      </c>
       <c r="X67" s="10" t="n"/>
       <c r="Y67" s="10" t="n"/>
       <c r="Z67" s="10" t="n"/>
@@ -5158,7 +5270,9 @@
       <c r="S68" s="10" t="n"/>
       <c r="U68" s="10" t="n"/>
       <c r="V68" s="10" t="n"/>
-      <c r="W68" s="10" t="n"/>
+      <c r="W68" s="10" t="n">
+        <v>423</v>
+      </c>
       <c r="X68" s="10" t="n"/>
       <c r="Y68" s="10" t="n"/>
       <c r="Z68" s="10" t="n"/>
@@ -5215,7 +5329,9 @@
       <c r="S69" s="10" t="n"/>
       <c r="U69" s="10" t="n"/>
       <c r="V69" s="10" t="n"/>
-      <c r="W69" s="10" t="n"/>
+      <c r="W69" s="10" t="n">
+        <v>423</v>
+      </c>
       <c r="X69" s="10" t="n"/>
       <c r="Y69" s="10" t="n"/>
       <c r="Z69" s="10" t="n"/>
@@ -5272,7 +5388,9 @@
       <c r="S70" s="10" t="n"/>
       <c r="U70" s="10" t="n"/>
       <c r="V70" s="10" t="n"/>
-      <c r="W70" s="10" t="n"/>
+      <c r="W70" s="10" t="n">
+        <v>423</v>
+      </c>
       <c r="X70" s="10" t="n"/>
       <c r="Y70" s="10" t="n"/>
       <c r="Z70" s="10" t="n"/>
@@ -5329,7 +5447,9 @@
       <c r="S71" s="10" t="n"/>
       <c r="U71" s="10" t="n"/>
       <c r="V71" s="10" t="n"/>
-      <c r="W71" s="10" t="n"/>
+      <c r="W71" s="10" t="n">
+        <v>423</v>
+      </c>
       <c r="X71" s="10" t="n"/>
       <c r="Y71" s="10" t="n"/>
       <c r="Z71" s="10" t="n"/>
@@ -5386,7 +5506,9 @@
       <c r="S72" s="10" t="n"/>
       <c r="U72" s="10" t="n"/>
       <c r="V72" s="10" t="n"/>
-      <c r="W72" s="10" t="n"/>
+      <c r="W72" s="10" t="n">
+        <v>423</v>
+      </c>
       <c r="X72" s="10" t="n"/>
       <c r="Y72" s="10" t="n"/>
       <c r="Z72" s="10" t="n"/>
@@ -5443,7 +5565,9 @@
       <c r="S73" s="10" t="n"/>
       <c r="U73" s="10" t="n"/>
       <c r="V73" s="10" t="n"/>
-      <c r="W73" s="10" t="n"/>
+      <c r="W73" s="10" t="n">
+        <v>423</v>
+      </c>
       <c r="X73" s="10" t="n"/>
       <c r="Y73" s="10" t="n"/>
       <c r="Z73" s="10" t="n"/>
@@ -5500,7 +5624,9 @@
       <c r="S74" s="10" t="n"/>
       <c r="U74" s="10" t="n"/>
       <c r="V74" s="10" t="n"/>
-      <c r="W74" s="10" t="n"/>
+      <c r="W74" s="10" t="n">
+        <v>423</v>
+      </c>
       <c r="X74" s="10" t="n"/>
       <c r="Y74" s="10" t="n"/>
       <c r="Z74" s="10" t="n"/>
@@ -5557,7 +5683,9 @@
       <c r="S75" s="10" t="n"/>
       <c r="U75" s="10" t="n"/>
       <c r="V75" s="10" t="n"/>
-      <c r="W75" s="10" t="n"/>
+      <c r="W75" s="10" t="n">
+        <v>423</v>
+      </c>
       <c r="X75" s="10" t="n"/>
       <c r="Y75" s="10" t="n"/>
       <c r="Z75" s="10" t="n"/>
@@ -5614,7 +5742,9 @@
       <c r="S76" s="10" t="n"/>
       <c r="U76" s="10" t="n"/>
       <c r="V76" s="10" t="n"/>
-      <c r="W76" s="10" t="n"/>
+      <c r="W76" s="10" t="n">
+        <v>423</v>
+      </c>
       <c r="X76" s="10" t="n"/>
       <c r="Y76" s="10" t="n"/>
       <c r="Z76" s="10" t="n"/>
@@ -5671,7 +5801,9 @@
       <c r="S77" s="10" t="n"/>
       <c r="U77" s="10" t="n"/>
       <c r="V77" s="10" t="n"/>
-      <c r="W77" s="10" t="n"/>
+      <c r="W77" s="10" t="n">
+        <v>423</v>
+      </c>
       <c r="X77" s="10" t="n"/>
       <c r="Y77" s="10" t="n"/>
       <c r="Z77" s="10" t="n"/>
@@ -5728,7 +5860,9 @@
       <c r="S78" s="10" t="n"/>
       <c r="U78" s="10" t="n"/>
       <c r="V78" s="10" t="n"/>
-      <c r="W78" s="10" t="n"/>
+      <c r="W78" s="10" t="n">
+        <v>423</v>
+      </c>
       <c r="X78" s="10" t="n"/>
       <c r="Y78" s="10" t="n"/>
       <c r="Z78" s="10" t="n"/>
@@ -5785,7 +5919,9 @@
       <c r="S79" s="10" t="n"/>
       <c r="U79" s="10" t="n"/>
       <c r="V79" s="10" t="n"/>
-      <c r="W79" s="10" t="n"/>
+      <c r="W79" s="10" t="n">
+        <v>423</v>
+      </c>
       <c r="X79" s="10" t="n"/>
       <c r="Y79" s="10" t="n">
         <v>200</v>
@@ -5844,7 +5980,9 @@
       <c r="S80" s="10" t="n"/>
       <c r="U80" s="10" t="n"/>
       <c r="V80" s="10" t="n"/>
-      <c r="W80" s="10" t="n"/>
+      <c r="W80" s="10" t="n">
+        <v>423</v>
+      </c>
       <c r="X80" s="10" t="n"/>
       <c r="Y80" s="10" t="n"/>
       <c r="Z80" s="10" t="n"/>
@@ -5901,7 +6039,9 @@
       <c r="S81" s="10" t="n"/>
       <c r="U81" s="10" t="n"/>
       <c r="V81" s="10" t="n"/>
-      <c r="W81" s="10" t="n"/>
+      <c r="W81" s="10" t="n">
+        <v>423</v>
+      </c>
       <c r="X81" s="10" t="n"/>
       <c r="Y81" s="10" t="n"/>
       <c r="Z81" s="10" t="n"/>
@@ -5958,7 +6098,9 @@
       <c r="S82" s="10" t="n"/>
       <c r="U82" s="10" t="n"/>
       <c r="V82" s="10" t="n"/>
-      <c r="W82" s="10" t="n"/>
+      <c r="W82" s="10" t="n">
+        <v>423</v>
+      </c>
       <c r="X82" s="10" t="n"/>
       <c r="Y82" s="10" t="n"/>
       <c r="Z82" s="10" t="n"/>
@@ -6015,7 +6157,9 @@
       <c r="S83" s="10" t="n"/>
       <c r="U83" s="10" t="n"/>
       <c r="V83" s="10" t="n"/>
-      <c r="W83" s="10" t="n"/>
+      <c r="W83" s="10" t="n">
+        <v>423</v>
+      </c>
       <c r="X83" s="10" t="n"/>
       <c r="Y83" s="10" t="n"/>
       <c r="Z83" s="10" t="n"/>
@@ -6072,7 +6216,9 @@
       <c r="S84" s="10" t="n"/>
       <c r="U84" s="10" t="n"/>
       <c r="V84" s="10" t="n"/>
-      <c r="W84" s="10" t="n"/>
+      <c r="W84" s="10" t="n">
+        <v>423</v>
+      </c>
       <c r="X84" s="10" t="n"/>
       <c r="Y84" s="10" t="n"/>
       <c r="Z84" s="10" t="n"/>
@@ -6129,7 +6275,9 @@
       <c r="S85" s="10" t="n"/>
       <c r="U85" s="10" t="n"/>
       <c r="V85" s="10" t="n"/>
-      <c r="W85" s="10" t="n"/>
+      <c r="W85" s="10" t="n">
+        <v>423</v>
+      </c>
       <c r="X85" s="10" t="n"/>
       <c r="Y85" s="10" t="n"/>
       <c r="Z85" s="10" t="n"/>
@@ -6186,7 +6334,9 @@
       <c r="S86" s="10" t="n"/>
       <c r="U86" s="10" t="n"/>
       <c r="V86" s="10" t="n"/>
-      <c r="W86" s="10" t="n"/>
+      <c r="W86" s="10" t="n">
+        <v>423</v>
+      </c>
       <c r="X86" s="10" t="n"/>
       <c r="Y86" s="10" t="n"/>
       <c r="Z86" s="10" t="n"/>
@@ -6243,7 +6393,9 @@
       <c r="S87" s="10" t="n"/>
       <c r="U87" s="10" t="n"/>
       <c r="V87" s="10" t="n"/>
-      <c r="W87" s="10" t="n"/>
+      <c r="W87" s="10" t="n">
+        <v>423</v>
+      </c>
       <c r="X87" s="10" t="n"/>
       <c r="Y87" s="10" t="n"/>
       <c r="Z87" s="10" t="n"/>
@@ -6300,7 +6452,9 @@
       <c r="S88" s="10" t="n"/>
       <c r="U88" s="10" t="n"/>
       <c r="V88" s="10" t="n"/>
-      <c r="W88" s="10" t="n"/>
+      <c r="W88" s="10" t="n">
+        <v>423</v>
+      </c>
       <c r="X88" s="10" t="n"/>
       <c r="Y88" s="10" t="n"/>
       <c r="Z88" s="10" t="n"/>
@@ -6357,7 +6511,9 @@
       <c r="S89" s="10" t="n"/>
       <c r="U89" s="10" t="n"/>
       <c r="V89" s="10" t="n"/>
-      <c r="W89" s="10" t="n"/>
+      <c r="W89" s="10" t="n">
+        <v>423</v>
+      </c>
       <c r="X89" s="10" t="n"/>
       <c r="Y89" s="10" t="n"/>
       <c r="Z89" s="10" t="n"/>
@@ -6414,7 +6570,9 @@
       <c r="S90" s="10" t="n"/>
       <c r="U90" s="10" t="n"/>
       <c r="V90" s="10" t="n"/>
-      <c r="W90" s="10" t="n"/>
+      <c r="W90" s="10" t="n">
+        <v>423</v>
+      </c>
       <c r="X90" s="10" t="n"/>
       <c r="Y90" s="10" t="n"/>
       <c r="Z90" s="10" t="n"/>
@@ -6471,7 +6629,9 @@
       <c r="S91" s="10" t="n"/>
       <c r="U91" s="10" t="n"/>
       <c r="V91" s="10" t="n"/>
-      <c r="W91" s="10" t="n"/>
+      <c r="W91" s="10" t="n">
+        <v>423</v>
+      </c>
       <c r="X91" s="10" t="n"/>
       <c r="Y91" s="10" t="n"/>
       <c r="Z91" s="10" t="n"/>
@@ -6528,7 +6688,9 @@
       <c r="S92" s="10" t="n"/>
       <c r="U92" s="10" t="n"/>
       <c r="V92" s="10" t="n"/>
-      <c r="W92" s="10" t="n"/>
+      <c r="W92" s="10" t="n">
+        <v>423</v>
+      </c>
       <c r="X92" s="10" t="n"/>
       <c r="Y92" s="10" t="n"/>
       <c r="Z92" s="10" t="n"/>
@@ -6585,7 +6747,9 @@
       <c r="S93" s="10" t="n"/>
       <c r="U93" s="10" t="n"/>
       <c r="V93" s="10" t="n"/>
-      <c r="W93" s="10" t="n"/>
+      <c r="W93" s="10" t="n">
+        <v>423</v>
+      </c>
       <c r="X93" s="10" t="n"/>
       <c r="Y93" s="10" t="n"/>
       <c r="Z93" s="10" t="n"/>
@@ -6642,7 +6806,9 @@
       <c r="S94" s="10" t="n"/>
       <c r="U94" s="10" t="n"/>
       <c r="V94" s="10" t="n"/>
-      <c r="W94" s="10" t="n"/>
+      <c r="W94" s="10" t="n">
+        <v>423</v>
+      </c>
       <c r="X94" s="10" t="n"/>
       <c r="Y94" s="10" t="n"/>
       <c r="Z94" s="10" t="n"/>
@@ -6699,7 +6865,9 @@
       <c r="S95" s="10" t="n"/>
       <c r="U95" s="10" t="n"/>
       <c r="V95" s="10" t="n"/>
-      <c r="W95" s="10" t="n"/>
+      <c r="W95" s="10" t="n">
+        <v>423</v>
+      </c>
       <c r="X95" s="10" t="n"/>
       <c r="Y95" s="10" t="n"/>
       <c r="Z95" s="10" t="n"/>
@@ -6756,7 +6924,9 @@
       <c r="S96" s="10" t="n"/>
       <c r="U96" s="10" t="n"/>
       <c r="V96" s="10" t="n"/>
-      <c r="W96" s="10" t="n"/>
+      <c r="W96" s="10" t="n">
+        <v>423</v>
+      </c>
       <c r="X96" s="10" t="n"/>
       <c r="Y96" s="10" t="n"/>
       <c r="Z96" s="10" t="n"/>
@@ -6813,7 +6983,9 @@
       <c r="S97" s="10" t="n"/>
       <c r="U97" s="10" t="n"/>
       <c r="V97" s="10" t="n"/>
-      <c r="W97" s="10" t="n"/>
+      <c r="W97" s="10" t="n">
+        <v>423</v>
+      </c>
       <c r="X97" s="10" t="n"/>
       <c r="Y97" s="10" t="n"/>
       <c r="Z97" s="10" t="n"/>
@@ -6870,7 +7042,9 @@
       <c r="S98" s="10" t="n"/>
       <c r="U98" s="10" t="n"/>
       <c r="V98" s="10" t="n"/>
-      <c r="W98" s="10" t="n"/>
+      <c r="W98" s="10" t="n">
+        <v>423</v>
+      </c>
       <c r="X98" s="10" t="n"/>
       <c r="Y98" s="10" t="n"/>
       <c r="Z98" s="10" t="n"/>
@@ -6927,7 +7101,9 @@
       <c r="S99" s="10" t="n"/>
       <c r="U99" s="10" t="n"/>
       <c r="V99" s="10" t="n"/>
-      <c r="W99" s="10" t="n"/>
+      <c r="W99" s="10" t="n">
+        <v>423</v>
+      </c>
       <c r="X99" s="10" t="n"/>
       <c r="Y99" s="10" t="n"/>
       <c r="Z99" s="10" t="n"/>
@@ -6984,7 +7160,9 @@
       <c r="S100" s="10" t="n"/>
       <c r="U100" s="10" t="n"/>
       <c r="V100" s="10" t="n"/>
-      <c r="W100" s="10" t="n"/>
+      <c r="W100" s="10" t="n">
+        <v>423</v>
+      </c>
       <c r="X100" s="10" t="n"/>
       <c r="Y100" s="10" t="n"/>
       <c r="Z100" s="10" t="n"/>
@@ -7041,7 +7219,9 @@
       <c r="S101" s="10" t="n"/>
       <c r="U101" s="10" t="n"/>
       <c r="V101" s="10" t="n"/>
-      <c r="W101" s="10" t="n"/>
+      <c r="W101" s="10" t="n">
+        <v>423</v>
+      </c>
       <c r="X101" s="10" t="n"/>
       <c r="Y101" s="10" t="n"/>
       <c r="Z101" s="10" t="n"/>
@@ -7098,7 +7278,9 @@
       <c r="S102" s="10" t="n"/>
       <c r="U102" s="10" t="n"/>
       <c r="V102" s="10" t="n"/>
-      <c r="W102" s="10" t="n"/>
+      <c r="W102" s="10" t="n">
+        <v>423</v>
+      </c>
       <c r="X102" s="10" t="n"/>
       <c r="Y102" s="10" t="n"/>
       <c r="Z102" s="10" t="n"/>
@@ -7155,7 +7337,9 @@
       <c r="S103" s="10" t="n"/>
       <c r="U103" s="10" t="n"/>
       <c r="V103" s="10" t="n"/>
-      <c r="W103" s="10" t="n"/>
+      <c r="W103" s="10" t="n">
+        <v>423</v>
+      </c>
       <c r="X103" s="10" t="n"/>
       <c r="Y103" s="10" t="n"/>
       <c r="Z103" s="10" t="n"/>
@@ -7212,7 +7396,9 @@
       <c r="S104" s="10" t="n"/>
       <c r="U104" s="10" t="n"/>
       <c r="V104" s="10" t="n"/>
-      <c r="W104" s="10" t="n"/>
+      <c r="W104" s="10" t="n">
+        <v>423</v>
+      </c>
       <c r="X104" s="10" t="n"/>
       <c r="Y104" s="10" t="n"/>
       <c r="Z104" s="10" t="n"/>
@@ -7269,7 +7455,9 @@
       <c r="S105" s="10" t="n"/>
       <c r="U105" s="10" t="n"/>
       <c r="V105" s="10" t="n"/>
-      <c r="W105" s="10" t="n"/>
+      <c r="W105" s="10" t="n">
+        <v>423</v>
+      </c>
       <c r="X105" s="10" t="n"/>
       <c r="Y105" s="10" t="n"/>
       <c r="Z105" s="10" t="n"/>
@@ -7326,10 +7514,242 @@
       <c r="S106" s="10" t="n"/>
       <c r="U106" s="10" t="n"/>
       <c r="V106" s="10" t="n"/>
-      <c r="W106" s="10" t="n"/>
+      <c r="W106" s="10" t="n">
+        <v>423</v>
+      </c>
       <c r="X106" s="10" t="n"/>
       <c r="Y106" s="10" t="n"/>
       <c r="Z106" s="10" t="n"/>
+    </row>
+    <row r="107">
+      <c r="E107" t="n">
+        <v>305</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>1 operator, 1 helper, 1/11 foreman</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>01- soft rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>sand and gravel</t>
+        </is>
+      </c>
+      <c r="K107" t="n">
+        <v>1</v>
+      </c>
+      <c r="L107" t="n">
+        <v>120</v>
+      </c>
+      <c r="M107" t="n">
+        <v>1</v>
+      </c>
+      <c r="N107" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="Q107" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R107" t="n">
+        <v>471</v>
+      </c>
+      <c r="W107" t="n">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="E108" t="n">
+        <v>305</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>1 operator, 1 helper, 1/11 foreman</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>01- soft rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>sand and gravel</t>
+        </is>
+      </c>
+      <c r="K108" t="n">
+        <v>1</v>
+      </c>
+      <c r="L108" t="n">
+        <v>120</v>
+      </c>
+      <c r="M108" t="n">
+        <v>1</v>
+      </c>
+      <c r="N108" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="Q108" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R108" t="n">
+        <v>471</v>
+      </c>
+      <c r="W108" t="n">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="E109" t="n">
+        <v>305</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>1 operator, 1 helper, 1/11 foreman</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>01- soft rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>sand and gravel</t>
+        </is>
+      </c>
+      <c r="K109" t="n">
+        <v>1</v>
+      </c>
+      <c r="L109" t="n">
+        <v>120</v>
+      </c>
+      <c r="M109" t="n">
+        <v>1</v>
+      </c>
+      <c r="N109" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="Q109" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R109" t="n">
+        <v>471</v>
+      </c>
+      <c r="W109" t="n">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="E110" t="n">
+        <v>305</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>1 operator, 1 helper, 1/11 foreman</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>01- soft rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>sand and gravel</t>
+        </is>
+      </c>
+      <c r="K110" t="n">
+        <v>1</v>
+      </c>
+      <c r="L110" t="n">
+        <v>120</v>
+      </c>
+      <c r="M110" t="n">
+        <v>1</v>
+      </c>
+      <c r="N110" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="Q110" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R110" t="n">
+        <v>471</v>
+      </c>
+      <c r="W110" t="n">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="E111" t="n">
+        <v>305</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>1 operator, 1 helper, 1/11 foreman</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Hoe</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>01- soft rock excavation using hydraulic excavator</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>sand and gravel</t>
+        </is>
+      </c>
+      <c r="K111" t="n">
+        <v>1</v>
+      </c>
+      <c r="L111" t="n">
+        <v>120</v>
+      </c>
+      <c r="M111" t="n">
+        <v>1</v>
+      </c>
+      <c r="N111" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="Q111" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R111" t="n">
+        <v>471</v>
+      </c>
+      <c r="W111" t="n">
+        <v>423</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -12345,7 +12765,7 @@
       </c>
       <c r="H21" s="69" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="I21" s="67" t="n"/>

--- a/P012-excavator-split_data_files/17_05_2017_cherinet_bisetegn _excavator_records_part_4.xlsx
+++ b/P012-excavator-split_data_files/17_05_2017_cherinet_bisetegn _excavator_records_part_4.xlsx
@@ -1170,7 +1170,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z111"/>
+  <dimension ref="A1:Z106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11.875" customWidth="1" min="1" max="1"/>
@@ -1628,10 +1628,22 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="n"/>
-      <c r="B7" s="18" t="n"/>
-      <c r="C7" s="18" t="n"/>
-      <c r="D7" s="18" t="n"/>
+      <c r="A7" s="18" t="inlineStr">
+        <is>
+          <t>17-05-2017</t>
+        </is>
+      </c>
+      <c r="B7" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" s="18" t="inlineStr">
+        <is>
+          <t>Cherinet Bisetegn</t>
+        </is>
+      </c>
+      <c r="D7" s="18" t="n">
+        <v>2</v>
+      </c>
       <c r="E7" s="19" t="n">
         <v>301</v>
       </c>
@@ -1966,9 +1978,7 @@
       <c r="S12" s="10" t="n"/>
       <c r="U12" s="10" t="n"/>
       <c r="V12" s="10" t="n"/>
-      <c r="W12" s="10" t="n">
-        <v>423</v>
-      </c>
+      <c r="W12" s="10" t="n"/>
       <c r="X12" s="10" t="n"/>
       <c r="Y12" s="10" t="n"/>
       <c r="Z12" s="10" t="n"/>
@@ -2025,9 +2035,7 @@
       <c r="S13" s="10" t="n"/>
       <c r="U13" s="10" t="n"/>
       <c r="V13" s="10" t="n"/>
-      <c r="W13" s="10" t="n">
-        <v>423</v>
-      </c>
+      <c r="W13" s="10" t="n"/>
       <c r="X13" s="10" t="n"/>
       <c r="Y13" s="10" t="n"/>
       <c r="Z13" s="10" t="n"/>
@@ -2084,9 +2092,7 @@
       <c r="S14" s="10" t="n"/>
       <c r="U14" s="10" t="n"/>
       <c r="V14" s="10" t="n"/>
-      <c r="W14" s="10" t="n">
-        <v>423</v>
-      </c>
+      <c r="W14" s="10" t="n"/>
       <c r="X14" s="10" t="n"/>
       <c r="Y14" s="10" t="n"/>
       <c r="Z14" s="10" t="n"/>
@@ -2143,9 +2149,7 @@
       <c r="S15" s="10" t="n"/>
       <c r="U15" s="10" t="n"/>
       <c r="V15" s="10" t="n"/>
-      <c r="W15" s="10" t="n">
-        <v>423</v>
-      </c>
+      <c r="W15" s="10" t="n"/>
       <c r="X15" s="10" t="n"/>
       <c r="Y15" s="10" t="n"/>
       <c r="Z15" s="10" t="n"/>
@@ -2202,9 +2206,7 @@
       <c r="S16" s="10" t="n"/>
       <c r="U16" s="10" t="n"/>
       <c r="V16" s="10" t="n"/>
-      <c r="W16" s="10" t="n">
-        <v>423</v>
-      </c>
+      <c r="W16" s="10" t="n"/>
       <c r="X16" s="10" t="n"/>
       <c r="Y16" s="10" t="n"/>
       <c r="Z16" s="10" t="n"/>
@@ -2261,9 +2263,7 @@
       <c r="S17" s="10" t="n"/>
       <c r="U17" s="10" t="n"/>
       <c r="V17" s="10" t="n"/>
-      <c r="W17" s="10" t="n">
-        <v>423</v>
-      </c>
+      <c r="W17" s="10" t="n"/>
       <c r="X17" s="10" t="n"/>
       <c r="Y17" s="10" t="n"/>
       <c r="Z17" s="10" t="n"/>
@@ -2320,9 +2320,7 @@
       <c r="S18" s="10" t="n"/>
       <c r="U18" s="10" t="n"/>
       <c r="V18" s="10" t="n"/>
-      <c r="W18" s="10" t="n">
-        <v>423</v>
-      </c>
+      <c r="W18" s="10" t="n"/>
       <c r="X18" s="10" t="n"/>
       <c r="Y18" s="10" t="n"/>
       <c r="Z18" s="10" t="n"/>
@@ -2379,9 +2377,7 @@
       <c r="S19" s="10" t="n"/>
       <c r="U19" s="10" t="n"/>
       <c r="V19" s="10" t="n"/>
-      <c r="W19" s="10" t="n">
-        <v>423</v>
-      </c>
+      <c r="W19" s="10" t="n"/>
       <c r="X19" s="10" t="n"/>
       <c r="Y19" s="10" t="n"/>
       <c r="Z19" s="10" t="n"/>
@@ -2438,9 +2434,7 @@
       <c r="S20" s="10" t="n"/>
       <c r="U20" s="10" t="n"/>
       <c r="V20" s="10" t="n"/>
-      <c r="W20" s="10" t="n">
-        <v>423</v>
-      </c>
+      <c r="W20" s="10" t="n"/>
       <c r="X20" s="10" t="n"/>
       <c r="Y20" s="10" t="n"/>
       <c r="Z20" s="10" t="n"/>
@@ -2497,9 +2491,7 @@
       <c r="S21" s="10" t="n"/>
       <c r="U21" s="10" t="n"/>
       <c r="V21" s="10" t="n"/>
-      <c r="W21" s="10" t="n">
-        <v>423</v>
-      </c>
+      <c r="W21" s="10" t="n"/>
       <c r="X21" s="10" t="n"/>
       <c r="Y21" s="10" t="n"/>
       <c r="Z21" s="10" t="n"/>
@@ -2556,9 +2548,7 @@
       <c r="S22" s="10" t="n"/>
       <c r="U22" s="10" t="n"/>
       <c r="V22" s="10" t="n"/>
-      <c r="W22" s="10" t="n">
-        <v>423</v>
-      </c>
+      <c r="W22" s="10" t="n"/>
       <c r="X22" s="10" t="n"/>
       <c r="Y22" s="10" t="n"/>
       <c r="Z22" s="10" t="n"/>
@@ -2615,9 +2605,7 @@
       <c r="S23" s="10" t="n"/>
       <c r="U23" s="10" t="n"/>
       <c r="V23" s="10" t="n"/>
-      <c r="W23" s="10" t="n">
-        <v>423</v>
-      </c>
+      <c r="W23" s="10" t="n"/>
       <c r="X23" s="10" t="n"/>
       <c r="Y23" s="10" t="n"/>
       <c r="Z23" s="10" t="n"/>
@@ -2674,9 +2662,7 @@
       <c r="S24" s="10" t="n"/>
       <c r="U24" s="10" t="n"/>
       <c r="V24" s="10" t="n"/>
-      <c r="W24" s="10" t="n">
-        <v>423</v>
-      </c>
+      <c r="W24" s="10" t="n"/>
       <c r="X24" s="10" t="n"/>
       <c r="Y24" s="10" t="n"/>
       <c r="Z24" s="10" t="n"/>
@@ -2733,9 +2719,7 @@
       <c r="S25" s="10" t="n"/>
       <c r="U25" s="10" t="n"/>
       <c r="V25" s="10" t="n"/>
-      <c r="W25" s="10" t="n">
-        <v>423</v>
-      </c>
+      <c r="W25" s="10" t="n"/>
       <c r="X25" s="10" t="n"/>
       <c r="Y25" s="10" t="n"/>
       <c r="Z25" s="10" t="n"/>
@@ -2792,9 +2776,7 @@
       <c r="S26" s="10" t="n"/>
       <c r="U26" s="10" t="n"/>
       <c r="V26" s="10" t="n"/>
-      <c r="W26" s="10" t="n">
-        <v>423</v>
-      </c>
+      <c r="W26" s="10" t="n"/>
       <c r="X26" s="10" t="n"/>
       <c r="Y26" s="10" t="n"/>
       <c r="Z26" s="10" t="n"/>
@@ -2851,9 +2833,7 @@
       <c r="S27" s="10" t="n"/>
       <c r="U27" s="10" t="n"/>
       <c r="V27" s="10" t="n"/>
-      <c r="W27" s="10" t="n">
-        <v>423</v>
-      </c>
+      <c r="W27" s="10" t="n"/>
       <c r="X27" s="10" t="n"/>
       <c r="Y27" s="10" t="n"/>
       <c r="Z27" s="10" t="n"/>
@@ -2910,9 +2890,7 @@
       <c r="S28" s="10" t="n"/>
       <c r="U28" s="10" t="n"/>
       <c r="V28" s="10" t="n"/>
-      <c r="W28" s="10" t="n">
-        <v>423</v>
-      </c>
+      <c r="W28" s="10" t="n"/>
       <c r="X28" s="10" t="n"/>
       <c r="Y28" s="10" t="n"/>
       <c r="Z28" s="10" t="n"/>
@@ -2969,9 +2947,7 @@
       <c r="S29" s="10" t="n"/>
       <c r="U29" s="10" t="n"/>
       <c r="V29" s="10" t="n"/>
-      <c r="W29" s="10" t="n">
-        <v>423</v>
-      </c>
+      <c r="W29" s="10" t="n"/>
       <c r="X29" s="10" t="n"/>
       <c r="Y29" s="10" t="n"/>
       <c r="Z29" s="10" t="n"/>
@@ -3028,9 +3004,7 @@
       <c r="S30" s="10" t="n"/>
       <c r="U30" s="10" t="n"/>
       <c r="V30" s="10" t="n"/>
-      <c r="W30" s="10" t="n">
-        <v>423</v>
-      </c>
+      <c r="W30" s="10" t="n"/>
       <c r="X30" s="10" t="n"/>
       <c r="Y30" s="10" t="n"/>
       <c r="Z30" s="10" t="n"/>
@@ -3087,9 +3061,7 @@
       <c r="S31" s="10" t="n"/>
       <c r="U31" s="10" t="n"/>
       <c r="V31" s="10" t="n"/>
-      <c r="W31" s="10" t="n">
-        <v>423</v>
-      </c>
+      <c r="W31" s="10" t="n"/>
       <c r="X31" s="10" t="n"/>
       <c r="Y31" s="10" t="n"/>
       <c r="Z31" s="10" t="n"/>
@@ -3146,9 +3118,7 @@
       <c r="S32" s="10" t="n"/>
       <c r="U32" s="10" t="n"/>
       <c r="V32" s="10" t="n"/>
-      <c r="W32" s="10" t="n">
-        <v>423</v>
-      </c>
+      <c r="W32" s="10" t="n"/>
       <c r="X32" s="10" t="n"/>
       <c r="Y32" s="10" t="n"/>
       <c r="Z32" s="10" t="n"/>
@@ -3205,9 +3175,7 @@
       <c r="S33" s="10" t="n"/>
       <c r="U33" s="10" t="n"/>
       <c r="V33" s="10" t="n"/>
-      <c r="W33" s="10" t="n">
-        <v>423</v>
-      </c>
+      <c r="W33" s="10" t="n"/>
       <c r="X33" s="10" t="n"/>
       <c r="Y33" s="10" t="n"/>
       <c r="Z33" s="10" t="n"/>
@@ -3264,9 +3232,7 @@
       <c r="S34" s="10" t="n"/>
       <c r="U34" s="10" t="n"/>
       <c r="V34" s="10" t="n"/>
-      <c r="W34" s="10" t="n">
-        <v>423</v>
-      </c>
+      <c r="W34" s="10" t="n"/>
       <c r="X34" s="10" t="n"/>
       <c r="Y34" s="10" t="n"/>
       <c r="Z34" s="10" t="n"/>
@@ -3323,9 +3289,7 @@
       <c r="S35" s="10" t="n"/>
       <c r="U35" s="10" t="n"/>
       <c r="V35" s="10" t="n"/>
-      <c r="W35" s="10" t="n">
-        <v>423</v>
-      </c>
+      <c r="W35" s="10" t="n"/>
       <c r="X35" s="10" t="n"/>
       <c r="Y35" s="10" t="n"/>
       <c r="Z35" s="10" t="n"/>
@@ -3382,9 +3346,7 @@
       <c r="S36" s="10" t="n"/>
       <c r="U36" s="10" t="n"/>
       <c r="V36" s="10" t="n"/>
-      <c r="W36" s="10" t="n">
-        <v>423</v>
-      </c>
+      <c r="W36" s="10" t="n"/>
       <c r="X36" s="10" t="n"/>
       <c r="Y36" s="10" t="n"/>
       <c r="Z36" s="10" t="n"/>
@@ -3441,9 +3403,7 @@
       <c r="S37" s="10" t="n"/>
       <c r="U37" s="10" t="n"/>
       <c r="V37" s="10" t="n"/>
-      <c r="W37" s="10" t="n">
-        <v>423</v>
-      </c>
+      <c r="W37" s="10" t="n"/>
       <c r="X37" s="10" t="n"/>
       <c r="Y37" s="10" t="n"/>
       <c r="Z37" s="10" t="n"/>
@@ -3500,9 +3460,7 @@
       <c r="S38" s="10" t="n"/>
       <c r="U38" s="10" t="n"/>
       <c r="V38" s="10" t="n"/>
-      <c r="W38" s="10" t="n">
-        <v>423</v>
-      </c>
+      <c r="W38" s="10" t="n"/>
       <c r="X38" s="10" t="n"/>
       <c r="Y38" s="10" t="n"/>
       <c r="Z38" s="10" t="n"/>
@@ -3559,9 +3517,7 @@
       <c r="S39" s="10" t="n"/>
       <c r="U39" s="10" t="n"/>
       <c r="V39" s="10" t="n"/>
-      <c r="W39" s="10" t="n">
-        <v>423</v>
-      </c>
+      <c r="W39" s="10" t="n"/>
       <c r="X39" s="10" t="n"/>
       <c r="Y39" s="10" t="n"/>
       <c r="Z39" s="10" t="n"/>
@@ -3618,9 +3574,7 @@
       <c r="S40" s="10" t="n"/>
       <c r="U40" s="10" t="n"/>
       <c r="V40" s="10" t="n"/>
-      <c r="W40" s="10" t="n">
-        <v>423</v>
-      </c>
+      <c r="W40" s="10" t="n"/>
       <c r="X40" s="10" t="n"/>
       <c r="Y40" s="10" t="n"/>
       <c r="Z40" s="10" t="n"/>
@@ -3677,9 +3631,7 @@
       <c r="S41" s="10" t="n"/>
       <c r="U41" s="10" t="n"/>
       <c r="V41" s="10" t="n"/>
-      <c r="W41" s="10" t="n">
-        <v>423</v>
-      </c>
+      <c r="W41" s="10" t="n"/>
       <c r="X41" s="10" t="n"/>
       <c r="Y41" s="10" t="n"/>
       <c r="Z41" s="10" t="n"/>
@@ -3736,9 +3688,7 @@
       <c r="S42" s="10" t="n"/>
       <c r="U42" s="10" t="n"/>
       <c r="V42" s="10" t="n"/>
-      <c r="W42" s="10" t="n">
-        <v>423</v>
-      </c>
+      <c r="W42" s="10" t="n"/>
       <c r="X42" s="10" t="n"/>
       <c r="Y42" s="10" t="n"/>
       <c r="Z42" s="10" t="n"/>
@@ -3795,9 +3745,7 @@
       <c r="S43" s="10" t="n"/>
       <c r="U43" s="10" t="n"/>
       <c r="V43" s="10" t="n"/>
-      <c r="W43" s="10" t="n">
-        <v>423</v>
-      </c>
+      <c r="W43" s="10" t="n"/>
       <c r="X43" s="10" t="n"/>
       <c r="Y43" s="10" t="n"/>
       <c r="Z43" s="10" t="n"/>
@@ -3854,9 +3802,7 @@
       <c r="S44" s="10" t="n"/>
       <c r="U44" s="10" t="n"/>
       <c r="V44" s="10" t="n"/>
-      <c r="W44" s="10" t="n">
-        <v>423</v>
-      </c>
+      <c r="W44" s="10" t="n"/>
       <c r="X44" s="10" t="n"/>
       <c r="Y44" s="10" t="n"/>
       <c r="Z44" s="10" t="n"/>
@@ -3913,9 +3859,7 @@
       <c r="S45" s="10" t="n"/>
       <c r="U45" s="10" t="n"/>
       <c r="V45" s="10" t="n"/>
-      <c r="W45" s="10" t="n">
-        <v>423</v>
-      </c>
+      <c r="W45" s="10" t="n"/>
       <c r="X45" s="10" t="n"/>
       <c r="Y45" s="10" t="n"/>
       <c r="Z45" s="10" t="n"/>
@@ -3972,9 +3916,7 @@
       <c r="S46" s="10" t="n"/>
       <c r="U46" s="10" t="n"/>
       <c r="V46" s="10" t="n"/>
-      <c r="W46" s="10" t="n">
-        <v>423</v>
-      </c>
+      <c r="W46" s="10" t="n"/>
       <c r="X46" s="10" t="n"/>
       <c r="Y46" s="10" t="n"/>
       <c r="Z46" s="10" t="n"/>
@@ -4031,9 +3973,7 @@
       <c r="S47" s="10" t="n"/>
       <c r="U47" s="10" t="n"/>
       <c r="V47" s="10" t="n"/>
-      <c r="W47" s="10" t="n">
-        <v>423</v>
-      </c>
+      <c r="W47" s="10" t="n"/>
       <c r="X47" s="10" t="n"/>
       <c r="Y47" s="10" t="n"/>
       <c r="Z47" s="10" t="n"/>
@@ -4090,9 +4030,7 @@
       <c r="S48" s="10" t="n"/>
       <c r="U48" s="10" t="n"/>
       <c r="V48" s="10" t="n"/>
-      <c r="W48" s="10" t="n">
-        <v>423</v>
-      </c>
+      <c r="W48" s="10" t="n"/>
       <c r="X48" s="10" t="n"/>
       <c r="Y48" s="10" t="n"/>
       <c r="Z48" s="10" t="n"/>
@@ -4149,9 +4087,7 @@
       <c r="S49" s="10" t="n"/>
       <c r="U49" s="10" t="n"/>
       <c r="V49" s="10" t="n"/>
-      <c r="W49" s="10" t="n">
-        <v>423</v>
-      </c>
+      <c r="W49" s="10" t="n"/>
       <c r="X49" s="10" t="n"/>
       <c r="Y49" s="10" t="n"/>
       <c r="Z49" s="10" t="n"/>
@@ -4208,9 +4144,7 @@
       <c r="S50" s="10" t="n"/>
       <c r="U50" s="10" t="n"/>
       <c r="V50" s="10" t="n"/>
-      <c r="W50" s="10" t="n">
-        <v>423</v>
-      </c>
+      <c r="W50" s="10" t="n"/>
       <c r="X50" s="10" t="n"/>
       <c r="Y50" s="10" t="n"/>
       <c r="Z50" s="10" t="n"/>
@@ -4267,9 +4201,7 @@
       <c r="S51" s="10" t="n"/>
       <c r="U51" s="10" t="n"/>
       <c r="V51" s="10" t="n"/>
-      <c r="W51" s="10" t="n">
-        <v>423</v>
-      </c>
+      <c r="W51" s="10" t="n"/>
       <c r="X51" s="10" t="n"/>
       <c r="Y51" s="10" t="n"/>
       <c r="Z51" s="10" t="n"/>
@@ -4326,9 +4258,7 @@
       <c r="S52" s="10" t="n"/>
       <c r="U52" s="10" t="n"/>
       <c r="V52" s="10" t="n"/>
-      <c r="W52" s="10" t="n">
-        <v>423</v>
-      </c>
+      <c r="W52" s="10" t="n"/>
       <c r="X52" s="10" t="n"/>
       <c r="Y52" s="10" t="n"/>
       <c r="Z52" s="10" t="n"/>
@@ -4385,9 +4315,7 @@
       <c r="S53" s="10" t="n"/>
       <c r="U53" s="10" t="n"/>
       <c r="V53" s="10" t="n"/>
-      <c r="W53" s="10" t="n">
-        <v>423</v>
-      </c>
+      <c r="W53" s="10" t="n"/>
       <c r="X53" s="10" t="n"/>
       <c r="Y53" s="10" t="n"/>
       <c r="Z53" s="10" t="n"/>
@@ -4444,9 +4372,7 @@
       <c r="S54" s="10" t="n"/>
       <c r="U54" s="10" t="n"/>
       <c r="V54" s="10" t="n"/>
-      <c r="W54" s="10" t="n">
-        <v>423</v>
-      </c>
+      <c r="W54" s="10" t="n"/>
       <c r="X54" s="10" t="n"/>
       <c r="Y54" s="10" t="n"/>
       <c r="Z54" s="10" t="n"/>
@@ -4503,9 +4429,7 @@
       <c r="S55" s="10" t="n"/>
       <c r="U55" s="10" t="n"/>
       <c r="V55" s="10" t="n"/>
-      <c r="W55" s="10" t="n">
-        <v>423</v>
-      </c>
+      <c r="W55" s="10" t="n"/>
       <c r="X55" s="10" t="n"/>
       <c r="Y55" s="10" t="n"/>
       <c r="Z55" s="10" t="n"/>
@@ -4562,9 +4486,7 @@
       <c r="S56" s="10" t="n"/>
       <c r="U56" s="10" t="n"/>
       <c r="V56" s="10" t="n"/>
-      <c r="W56" s="10" t="n">
-        <v>423</v>
-      </c>
+      <c r="W56" s="10" t="n"/>
       <c r="X56" s="10" t="n"/>
       <c r="Y56" s="10" t="n"/>
       <c r="Z56" s="10" t="n"/>
@@ -4621,9 +4543,7 @@
       <c r="S57" s="10" t="n"/>
       <c r="U57" s="10" t="n"/>
       <c r="V57" s="10" t="n"/>
-      <c r="W57" s="10" t="n">
-        <v>423</v>
-      </c>
+      <c r="W57" s="10" t="n"/>
       <c r="X57" s="10" t="n"/>
       <c r="Y57" s="10" t="n"/>
       <c r="Z57" s="10" t="n"/>
@@ -4680,9 +4600,7 @@
       <c r="S58" s="10" t="n"/>
       <c r="U58" s="10" t="n"/>
       <c r="V58" s="10" t="n"/>
-      <c r="W58" s="10" t="n">
-        <v>423</v>
-      </c>
+      <c r="W58" s="10" t="n"/>
       <c r="X58" s="10" t="n"/>
       <c r="Y58" s="10" t="n"/>
       <c r="Z58" s="10" t="n"/>
@@ -4739,9 +4657,7 @@
       <c r="S59" s="10" t="n"/>
       <c r="U59" s="10" t="n"/>
       <c r="V59" s="10" t="n"/>
-      <c r="W59" s="10" t="n">
-        <v>423</v>
-      </c>
+      <c r="W59" s="10" t="n"/>
       <c r="X59" s="10" t="n"/>
       <c r="Y59" s="10" t="n"/>
       <c r="Z59" s="10" t="n"/>
@@ -4798,9 +4714,7 @@
       <c r="S60" s="10" t="n"/>
       <c r="U60" s="10" t="n"/>
       <c r="V60" s="10" t="n"/>
-      <c r="W60" s="10" t="n">
-        <v>423</v>
-      </c>
+      <c r="W60" s="10" t="n"/>
       <c r="X60" s="10" t="n"/>
       <c r="Y60" s="10" t="n"/>
       <c r="Z60" s="10" t="n"/>
@@ -4857,9 +4771,7 @@
       <c r="S61" s="10" t="n"/>
       <c r="U61" s="10" t="n"/>
       <c r="V61" s="10" t="n"/>
-      <c r="W61" s="10" t="n">
-        <v>423</v>
-      </c>
+      <c r="W61" s="10" t="n"/>
       <c r="X61" s="10" t="n"/>
       <c r="Y61" s="10" t="n"/>
       <c r="Z61" s="10" t="n"/>
@@ -4916,9 +4828,7 @@
       <c r="S62" s="10" t="n"/>
       <c r="U62" s="10" t="n"/>
       <c r="V62" s="10" t="n"/>
-      <c r="W62" s="10" t="n">
-        <v>423</v>
-      </c>
+      <c r="W62" s="10" t="n"/>
       <c r="X62" s="10" t="n"/>
       <c r="Y62" s="10" t="n"/>
       <c r="Z62" s="10" t="n"/>
@@ -4975,9 +4885,7 @@
       <c r="S63" s="10" t="n"/>
       <c r="U63" s="10" t="n"/>
       <c r="V63" s="10" t="n"/>
-      <c r="W63" s="10" t="n">
-        <v>423</v>
-      </c>
+      <c r="W63" s="10" t="n"/>
       <c r="X63" s="10" t="n"/>
       <c r="Y63" s="10" t="n"/>
       <c r="Z63" s="10" t="n"/>
@@ -5034,9 +4942,7 @@
       <c r="S64" s="10" t="n"/>
       <c r="U64" s="10" t="n"/>
       <c r="V64" s="10" t="n"/>
-      <c r="W64" s="10" t="n">
-        <v>423</v>
-      </c>
+      <c r="W64" s="10" t="n"/>
       <c r="X64" s="10" t="n"/>
       <c r="Y64" s="10" t="n"/>
       <c r="Z64" s="10" t="n"/>
@@ -5093,9 +4999,7 @@
       <c r="S65" s="10" t="n"/>
       <c r="U65" s="10" t="n"/>
       <c r="V65" s="10" t="n"/>
-      <c r="W65" s="10" t="n">
-        <v>423</v>
-      </c>
+      <c r="W65" s="10" t="n"/>
       <c r="X65" s="10" t="n"/>
       <c r="Y65" s="10" t="n"/>
       <c r="Z65" s="10" t="n"/>
@@ -5152,9 +5056,7 @@
       <c r="S66" s="10" t="n"/>
       <c r="U66" s="10" t="n"/>
       <c r="V66" s="10" t="n"/>
-      <c r="W66" s="10" t="n">
-        <v>423</v>
-      </c>
+      <c r="W66" s="10" t="n"/>
       <c r="X66" s="10" t="n"/>
       <c r="Y66" s="10" t="n"/>
       <c r="Z66" s="10" t="n"/>
@@ -5211,9 +5113,7 @@
       <c r="S67" s="10" t="n"/>
       <c r="U67" s="10" t="n"/>
       <c r="V67" s="10" t="n"/>
-      <c r="W67" s="10" t="n">
-        <v>423</v>
-      </c>
+      <c r="W67" s="10" t="n"/>
       <c r="X67" s="10" t="n"/>
       <c r="Y67" s="10" t="n"/>
       <c r="Z67" s="10" t="n"/>
@@ -5270,9 +5170,7 @@
       <c r="S68" s="10" t="n"/>
       <c r="U68" s="10" t="n"/>
       <c r="V68" s="10" t="n"/>
-      <c r="W68" s="10" t="n">
-        <v>423</v>
-      </c>
+      <c r="W68" s="10" t="n"/>
       <c r="X68" s="10" t="n"/>
       <c r="Y68" s="10" t="n"/>
       <c r="Z68" s="10" t="n"/>
@@ -5329,9 +5227,7 @@
       <c r="S69" s="10" t="n"/>
       <c r="U69" s="10" t="n"/>
       <c r="V69" s="10" t="n"/>
-      <c r="W69" s="10" t="n">
-        <v>423</v>
-      </c>
+      <c r="W69" s="10" t="n"/>
       <c r="X69" s="10" t="n"/>
       <c r="Y69" s="10" t="n"/>
       <c r="Z69" s="10" t="n"/>
@@ -5388,9 +5284,7 @@
       <c r="S70" s="10" t="n"/>
       <c r="U70" s="10" t="n"/>
       <c r="V70" s="10" t="n"/>
-      <c r="W70" s="10" t="n">
-        <v>423</v>
-      </c>
+      <c r="W70" s="10" t="n"/>
       <c r="X70" s="10" t="n"/>
       <c r="Y70" s="10" t="n"/>
       <c r="Z70" s="10" t="n"/>
@@ -5447,9 +5341,7 @@
       <c r="S71" s="10" t="n"/>
       <c r="U71" s="10" t="n"/>
       <c r="V71" s="10" t="n"/>
-      <c r="W71" s="10" t="n">
-        <v>423</v>
-      </c>
+      <c r="W71" s="10" t="n"/>
       <c r="X71" s="10" t="n"/>
       <c r="Y71" s="10" t="n"/>
       <c r="Z71" s="10" t="n"/>
@@ -5506,9 +5398,7 @@
       <c r="S72" s="10" t="n"/>
       <c r="U72" s="10" t="n"/>
       <c r="V72" s="10" t="n"/>
-      <c r="W72" s="10" t="n">
-        <v>423</v>
-      </c>
+      <c r="W72" s="10" t="n"/>
       <c r="X72" s="10" t="n"/>
       <c r="Y72" s="10" t="n"/>
       <c r="Z72" s="10" t="n"/>
@@ -5565,9 +5455,7 @@
       <c r="S73" s="10" t="n"/>
       <c r="U73" s="10" t="n"/>
       <c r="V73" s="10" t="n"/>
-      <c r="W73" s="10" t="n">
-        <v>423</v>
-      </c>
+      <c r="W73" s="10" t="n"/>
       <c r="X73" s="10" t="n"/>
       <c r="Y73" s="10" t="n"/>
       <c r="Z73" s="10" t="n"/>
@@ -5624,9 +5512,7 @@
       <c r="S74" s="10" t="n"/>
       <c r="U74" s="10" t="n"/>
       <c r="V74" s="10" t="n"/>
-      <c r="W74" s="10" t="n">
-        <v>423</v>
-      </c>
+      <c r="W74" s="10" t="n"/>
       <c r="X74" s="10" t="n"/>
       <c r="Y74" s="10" t="n"/>
       <c r="Z74" s="10" t="n"/>
@@ -5683,9 +5569,7 @@
       <c r="S75" s="10" t="n"/>
       <c r="U75" s="10" t="n"/>
       <c r="V75" s="10" t="n"/>
-      <c r="W75" s="10" t="n">
-        <v>423</v>
-      </c>
+      <c r="W75" s="10" t="n"/>
       <c r="X75" s="10" t="n"/>
       <c r="Y75" s="10" t="n"/>
       <c r="Z75" s="10" t="n"/>
@@ -5742,9 +5626,7 @@
       <c r="S76" s="10" t="n"/>
       <c r="U76" s="10" t="n"/>
       <c r="V76" s="10" t="n"/>
-      <c r="W76" s="10" t="n">
-        <v>423</v>
-      </c>
+      <c r="W76" s="10" t="n"/>
       <c r="X76" s="10" t="n"/>
       <c r="Y76" s="10" t="n"/>
       <c r="Z76" s="10" t="n"/>
@@ -5801,9 +5683,7 @@
       <c r="S77" s="10" t="n"/>
       <c r="U77" s="10" t="n"/>
       <c r="V77" s="10" t="n"/>
-      <c r="W77" s="10" t="n">
-        <v>423</v>
-      </c>
+      <c r="W77" s="10" t="n"/>
       <c r="X77" s="10" t="n"/>
       <c r="Y77" s="10" t="n"/>
       <c r="Z77" s="10" t="n"/>
@@ -5860,9 +5740,7 @@
       <c r="S78" s="10" t="n"/>
       <c r="U78" s="10" t="n"/>
       <c r="V78" s="10" t="n"/>
-      <c r="W78" s="10" t="n">
-        <v>423</v>
-      </c>
+      <c r="W78" s="10" t="n"/>
       <c r="X78" s="10" t="n"/>
       <c r="Y78" s="10" t="n"/>
       <c r="Z78" s="10" t="n"/>
@@ -5919,9 +5797,7 @@
       <c r="S79" s="10" t="n"/>
       <c r="U79" s="10" t="n"/>
       <c r="V79" s="10" t="n"/>
-      <c r="W79" s="10" t="n">
-        <v>423</v>
-      </c>
+      <c r="W79" s="10" t="n"/>
       <c r="X79" s="10" t="n"/>
       <c r="Y79" s="10" t="n">
         <v>200</v>
@@ -5980,9 +5856,7 @@
       <c r="S80" s="10" t="n"/>
       <c r="U80" s="10" t="n"/>
       <c r="V80" s="10" t="n"/>
-      <c r="W80" s="10" t="n">
-        <v>423</v>
-      </c>
+      <c r="W80" s="10" t="n"/>
       <c r="X80" s="10" t="n"/>
       <c r="Y80" s="10" t="n"/>
       <c r="Z80" s="10" t="n"/>
@@ -6039,9 +5913,7 @@
       <c r="S81" s="10" t="n"/>
       <c r="U81" s="10" t="n"/>
       <c r="V81" s="10" t="n"/>
-      <c r="W81" s="10" t="n">
-        <v>423</v>
-      </c>
+      <c r="W81" s="10" t="n"/>
       <c r="X81" s="10" t="n"/>
       <c r="Y81" s="10" t="n"/>
       <c r="Z81" s="10" t="n"/>
@@ -6098,9 +5970,7 @@
       <c r="S82" s="10" t="n"/>
       <c r="U82" s="10" t="n"/>
       <c r="V82" s="10" t="n"/>
-      <c r="W82" s="10" t="n">
-        <v>423</v>
-      </c>
+      <c r="W82" s="10" t="n"/>
       <c r="X82" s="10" t="n"/>
       <c r="Y82" s="10" t="n"/>
       <c r="Z82" s="10" t="n"/>
@@ -6157,9 +6027,7 @@
       <c r="S83" s="10" t="n"/>
       <c r="U83" s="10" t="n"/>
       <c r="V83" s="10" t="n"/>
-      <c r="W83" s="10" t="n">
-        <v>423</v>
-      </c>
+      <c r="W83" s="10" t="n"/>
       <c r="X83" s="10" t="n"/>
       <c r="Y83" s="10" t="n"/>
       <c r="Z83" s="10" t="n"/>
@@ -6216,9 +6084,7 @@
       <c r="S84" s="10" t="n"/>
       <c r="U84" s="10" t="n"/>
       <c r="V84" s="10" t="n"/>
-      <c r="W84" s="10" t="n">
-        <v>423</v>
-      </c>
+      <c r="W84" s="10" t="n"/>
       <c r="X84" s="10" t="n"/>
       <c r="Y84" s="10" t="n"/>
       <c r="Z84" s="10" t="n"/>
@@ -6275,9 +6141,7 @@
       <c r="S85" s="10" t="n"/>
       <c r="U85" s="10" t="n"/>
       <c r="V85" s="10" t="n"/>
-      <c r="W85" s="10" t="n">
-        <v>423</v>
-      </c>
+      <c r="W85" s="10" t="n"/>
       <c r="X85" s="10" t="n"/>
       <c r="Y85" s="10" t="n"/>
       <c r="Z85" s="10" t="n"/>
@@ -6334,9 +6198,7 @@
       <c r="S86" s="10" t="n"/>
       <c r="U86" s="10" t="n"/>
       <c r="V86" s="10" t="n"/>
-      <c r="W86" s="10" t="n">
-        <v>423</v>
-      </c>
+      <c r="W86" s="10" t="n"/>
       <c r="X86" s="10" t="n"/>
       <c r="Y86" s="10" t="n"/>
       <c r="Z86" s="10" t="n"/>
@@ -6393,9 +6255,7 @@
       <c r="S87" s="10" t="n"/>
       <c r="U87" s="10" t="n"/>
       <c r="V87" s="10" t="n"/>
-      <c r="W87" s="10" t="n">
-        <v>423</v>
-      </c>
+      <c r="W87" s="10" t="n"/>
       <c r="X87" s="10" t="n"/>
       <c r="Y87" s="10" t="n"/>
       <c r="Z87" s="10" t="n"/>
@@ -6452,9 +6312,7 @@
       <c r="S88" s="10" t="n"/>
       <c r="U88" s="10" t="n"/>
       <c r="V88" s="10" t="n"/>
-      <c r="W88" s="10" t="n">
-        <v>423</v>
-      </c>
+      <c r="W88" s="10" t="n"/>
       <c r="X88" s="10" t="n"/>
       <c r="Y88" s="10" t="n"/>
       <c r="Z88" s="10" t="n"/>
@@ -6511,9 +6369,7 @@
       <c r="S89" s="10" t="n"/>
       <c r="U89" s="10" t="n"/>
       <c r="V89" s="10" t="n"/>
-      <c r="W89" s="10" t="n">
-        <v>423</v>
-      </c>
+      <c r="W89" s="10" t="n"/>
       <c r="X89" s="10" t="n"/>
       <c r="Y89" s="10" t="n"/>
       <c r="Z89" s="10" t="n"/>
@@ -6570,9 +6426,7 @@
       <c r="S90" s="10" t="n"/>
       <c r="U90" s="10" t="n"/>
       <c r="V90" s="10" t="n"/>
-      <c r="W90" s="10" t="n">
-        <v>423</v>
-      </c>
+      <c r="W90" s="10" t="n"/>
       <c r="X90" s="10" t="n"/>
       <c r="Y90" s="10" t="n"/>
       <c r="Z90" s="10" t="n"/>
@@ -6629,9 +6483,7 @@
       <c r="S91" s="10" t="n"/>
       <c r="U91" s="10" t="n"/>
       <c r="V91" s="10" t="n"/>
-      <c r="W91" s="10" t="n">
-        <v>423</v>
-      </c>
+      <c r="W91" s="10" t="n"/>
       <c r="X91" s="10" t="n"/>
       <c r="Y91" s="10" t="n"/>
       <c r="Z91" s="10" t="n"/>
@@ -6688,9 +6540,7 @@
       <c r="S92" s="10" t="n"/>
       <c r="U92" s="10" t="n"/>
       <c r="V92" s="10" t="n"/>
-      <c r="W92" s="10" t="n">
-        <v>423</v>
-      </c>
+      <c r="W92" s="10" t="n"/>
       <c r="X92" s="10" t="n"/>
       <c r="Y92" s="10" t="n"/>
       <c r="Z92" s="10" t="n"/>
@@ -6747,9 +6597,7 @@
       <c r="S93" s="10" t="n"/>
       <c r="U93" s="10" t="n"/>
       <c r="V93" s="10" t="n"/>
-      <c r="W93" s="10" t="n">
-        <v>423</v>
-      </c>
+      <c r="W93" s="10" t="n"/>
       <c r="X93" s="10" t="n"/>
       <c r="Y93" s="10" t="n"/>
       <c r="Z93" s="10" t="n"/>
@@ -6806,9 +6654,7 @@
       <c r="S94" s="10" t="n"/>
       <c r="U94" s="10" t="n"/>
       <c r="V94" s="10" t="n"/>
-      <c r="W94" s="10" t="n">
-        <v>423</v>
-      </c>
+      <c r="W94" s="10" t="n"/>
       <c r="X94" s="10" t="n"/>
       <c r="Y94" s="10" t="n"/>
       <c r="Z94" s="10" t="n"/>
@@ -6865,9 +6711,7 @@
       <c r="S95" s="10" t="n"/>
       <c r="U95" s="10" t="n"/>
       <c r="V95" s="10" t="n"/>
-      <c r="W95" s="10" t="n">
-        <v>423</v>
-      </c>
+      <c r="W95" s="10" t="n"/>
       <c r="X95" s="10" t="n"/>
       <c r="Y95" s="10" t="n"/>
       <c r="Z95" s="10" t="n"/>
@@ -6924,9 +6768,7 @@
       <c r="S96" s="10" t="n"/>
       <c r="U96" s="10" t="n"/>
       <c r="V96" s="10" t="n"/>
-      <c r="W96" s="10" t="n">
-        <v>423</v>
-      </c>
+      <c r="W96" s="10" t="n"/>
       <c r="X96" s="10" t="n"/>
       <c r="Y96" s="10" t="n"/>
       <c r="Z96" s="10" t="n"/>
@@ -6983,9 +6825,7 @@
       <c r="S97" s="10" t="n"/>
       <c r="U97" s="10" t="n"/>
       <c r="V97" s="10" t="n"/>
-      <c r="W97" s="10" t="n">
-        <v>423</v>
-      </c>
+      <c r="W97" s="10" t="n"/>
       <c r="X97" s="10" t="n"/>
       <c r="Y97" s="10" t="n"/>
       <c r="Z97" s="10" t="n"/>
@@ -7042,9 +6882,7 @@
       <c r="S98" s="10" t="n"/>
       <c r="U98" s="10" t="n"/>
       <c r="V98" s="10" t="n"/>
-      <c r="W98" s="10" t="n">
-        <v>423</v>
-      </c>
+      <c r="W98" s="10" t="n"/>
       <c r="X98" s="10" t="n"/>
       <c r="Y98" s="10" t="n"/>
       <c r="Z98" s="10" t="n"/>
@@ -7101,9 +6939,7 @@
       <c r="S99" s="10" t="n"/>
       <c r="U99" s="10" t="n"/>
       <c r="V99" s="10" t="n"/>
-      <c r="W99" s="10" t="n">
-        <v>423</v>
-      </c>
+      <c r="W99" s="10" t="n"/>
       <c r="X99" s="10" t="n"/>
       <c r="Y99" s="10" t="n"/>
       <c r="Z99" s="10" t="n"/>
@@ -7160,9 +6996,7 @@
       <c r="S100" s="10" t="n"/>
       <c r="U100" s="10" t="n"/>
       <c r="V100" s="10" t="n"/>
-      <c r="W100" s="10" t="n">
-        <v>423</v>
-      </c>
+      <c r="W100" s="10" t="n"/>
       <c r="X100" s="10" t="n"/>
       <c r="Y100" s="10" t="n"/>
       <c r="Z100" s="10" t="n"/>
@@ -7219,9 +7053,7 @@
       <c r="S101" s="10" t="n"/>
       <c r="U101" s="10" t="n"/>
       <c r="V101" s="10" t="n"/>
-      <c r="W101" s="10" t="n">
-        <v>423</v>
-      </c>
+      <c r="W101" s="10" t="n"/>
       <c r="X101" s="10" t="n"/>
       <c r="Y101" s="10" t="n"/>
       <c r="Z101" s="10" t="n"/>
@@ -7278,9 +7110,7 @@
       <c r="S102" s="10" t="n"/>
       <c r="U102" s="10" t="n"/>
       <c r="V102" s="10" t="n"/>
-      <c r="W102" s="10" t="n">
-        <v>423</v>
-      </c>
+      <c r="W102" s="10" t="n"/>
       <c r="X102" s="10" t="n"/>
       <c r="Y102" s="10" t="n"/>
       <c r="Z102" s="10" t="n"/>
@@ -7337,9 +7167,7 @@
       <c r="S103" s="10" t="n"/>
       <c r="U103" s="10" t="n"/>
       <c r="V103" s="10" t="n"/>
-      <c r="W103" s="10" t="n">
-        <v>423</v>
-      </c>
+      <c r="W103" s="10" t="n"/>
       <c r="X103" s="10" t="n"/>
       <c r="Y103" s="10" t="n"/>
       <c r="Z103" s="10" t="n"/>
@@ -7396,9 +7224,7 @@
       <c r="S104" s="10" t="n"/>
       <c r="U104" s="10" t="n"/>
       <c r="V104" s="10" t="n"/>
-      <c r="W104" s="10" t="n">
-        <v>423</v>
-      </c>
+      <c r="W104" s="10" t="n"/>
       <c r="X104" s="10" t="n"/>
       <c r="Y104" s="10" t="n"/>
       <c r="Z104" s="10" t="n"/>
@@ -7455,9 +7281,7 @@
       <c r="S105" s="10" t="n"/>
       <c r="U105" s="10" t="n"/>
       <c r="V105" s="10" t="n"/>
-      <c r="W105" s="10" t="n">
-        <v>423</v>
-      </c>
+      <c r="W105" s="10" t="n"/>
       <c r="X105" s="10" t="n"/>
       <c r="Y105" s="10" t="n"/>
       <c r="Z105" s="10" t="n"/>
@@ -7514,242 +7338,10 @@
       <c r="S106" s="10" t="n"/>
       <c r="U106" s="10" t="n"/>
       <c r="V106" s="10" t="n"/>
-      <c r="W106" s="10" t="n">
-        <v>423</v>
-      </c>
+      <c r="W106" s="10" t="n"/>
       <c r="X106" s="10" t="n"/>
       <c r="Y106" s="10" t="n"/>
       <c r="Z106" s="10" t="n"/>
-    </row>
-    <row r="107">
-      <c r="E107" t="n">
-        <v>305</v>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>1 operator, 1 helper, 1/11 foreman</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>Hoe</t>
-        </is>
-      </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>01- soft rock excavation using hydraulic excavator</t>
-        </is>
-      </c>
-      <c r="J107" t="inlineStr">
-        <is>
-          <t>sand and gravel</t>
-        </is>
-      </c>
-      <c r="K107" t="n">
-        <v>1</v>
-      </c>
-      <c r="L107" t="n">
-        <v>120</v>
-      </c>
-      <c r="M107" t="n">
-        <v>1</v>
-      </c>
-      <c r="N107" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="Q107" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="R107" t="n">
-        <v>471</v>
-      </c>
-      <c r="W107" t="n">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="E108" t="n">
-        <v>305</v>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>1 operator, 1 helper, 1/11 foreman</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>Hoe</t>
-        </is>
-      </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>01- soft rock excavation using hydraulic excavator</t>
-        </is>
-      </c>
-      <c r="J108" t="inlineStr">
-        <is>
-          <t>sand and gravel</t>
-        </is>
-      </c>
-      <c r="K108" t="n">
-        <v>1</v>
-      </c>
-      <c r="L108" t="n">
-        <v>120</v>
-      </c>
-      <c r="M108" t="n">
-        <v>1</v>
-      </c>
-      <c r="N108" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="Q108" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="R108" t="n">
-        <v>471</v>
-      </c>
-      <c r="W108" t="n">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="E109" t="n">
-        <v>305</v>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>1 operator, 1 helper, 1/11 foreman</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>Hoe</t>
-        </is>
-      </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>01- soft rock excavation using hydraulic excavator</t>
-        </is>
-      </c>
-      <c r="J109" t="inlineStr">
-        <is>
-          <t>sand and gravel</t>
-        </is>
-      </c>
-      <c r="K109" t="n">
-        <v>1</v>
-      </c>
-      <c r="L109" t="n">
-        <v>120</v>
-      </c>
-      <c r="M109" t="n">
-        <v>1</v>
-      </c>
-      <c r="N109" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="Q109" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="R109" t="n">
-        <v>471</v>
-      </c>
-      <c r="W109" t="n">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="E110" t="n">
-        <v>305</v>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>1 operator, 1 helper, 1/11 foreman</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>Hoe</t>
-        </is>
-      </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>01- soft rock excavation using hydraulic excavator</t>
-        </is>
-      </c>
-      <c r="J110" t="inlineStr">
-        <is>
-          <t>sand and gravel</t>
-        </is>
-      </c>
-      <c r="K110" t="n">
-        <v>1</v>
-      </c>
-      <c r="L110" t="n">
-        <v>120</v>
-      </c>
-      <c r="M110" t="n">
-        <v>1</v>
-      </c>
-      <c r="N110" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="Q110" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="R110" t="n">
-        <v>471</v>
-      </c>
-      <c r="W110" t="n">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="E111" t="n">
-        <v>305</v>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>1 operator, 1 helper, 1/11 foreman</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>Hoe</t>
-        </is>
-      </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>01- soft rock excavation using hydraulic excavator</t>
-        </is>
-      </c>
-      <c r="J111" t="inlineStr">
-        <is>
-          <t>sand and gravel</t>
-        </is>
-      </c>
-      <c r="K111" t="n">
-        <v>1</v>
-      </c>
-      <c r="L111" t="n">
-        <v>120</v>
-      </c>
-      <c r="M111" t="n">
-        <v>1</v>
-      </c>
-      <c r="N111" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="Q111" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="R111" t="n">
-        <v>471</v>
-      </c>
-      <c r="W111" t="n">
-        <v>423</v>
-      </c>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -8159,7 +7751,7 @@
     <row r="7">
       <c r="A7" s="18" t="inlineStr">
         <is>
-          <t>17_05_2017</t>
+          <t>17-05-2017</t>
         </is>
       </c>
       <c r="B7" s="29" t="n">
